--- a/registration_forms/041_sports_club_vendor_booth_registration_form--registration_forms.xlsx
+++ b/registration_forms/041_sports_club_vendor_booth_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -789,12 +789,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>payment_details_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Payment Details</t>
+          <t>Payment Details 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vendor_needs</t>
+          <t>vendor_needs_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vendor Needs</t>
+          <t>Vendor Needs 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Vendor Needs Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Vendor Type Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1146,7 +1146,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1248,7 +1248,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vendor_needs_choices</t>
+          <t>vendor_needs_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vendor_needs_choices</t>
+          <t>vendor_needs_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
